--- a/Data/EXCEL/Transfer/salemon/20240711/3711-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/3711-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A36FEC0-814E-40B6-ABEE-305CFD11F0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{697ADE94-9E9D-4D77-A9B7-C6D03D06C041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{2B3F6DAF-D66E-4411-A733-FC221200DA34}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{41974988-F9DD-4143-B183-13F08CE91DA8}"/>
   </bookViews>
   <sheets>
     <sheet name="3711-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1267,22 +1267,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{239B512A-319C-446A-A0F7-F212CCCEBCF8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{482008FC-5108-4E39-B5F4-8F24CC4FA5A4}">
   <dimension ref="A1:Q159"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="5.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1309,7 +1309,7 @@
       <c r="P1" s="21"/>
       <c r="Q1" s="22"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="18"/>
       <c r="B2" s="17" t="s">
         <v>4</v>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Q2" s="22"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="18"/>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -1391,7 +1391,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="19"/>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -1430,7 +1430,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>45413</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1589,7 +1589,7 @@
         <v>2.5299999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>45352</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1695,7 +1695,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>45292</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1801,7 +1801,7 @@
         <v>-13.3</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>45231</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>-13.9</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>-14.4</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>45170</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>-14.6</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2013,7 +2013,7 @@
         <v>-13.8</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>45108</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>-13.1</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>-12.4</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>45047</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>-10.7</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>-9.75</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <v>44986</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>-9.34</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>-7.88</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>44927</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>-7.08</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>44866</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>44805</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>44743</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>23.9</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="11">
         <v>44682</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="11">
         <v>44621</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>44562</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>18.899999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <v>44501</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="11">
         <v>44440</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="11">
         <v>44378</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>20.9</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>20.2</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="11">
         <v>44317</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="11">
         <v>44256</v>
       </c>
@@ -3550,7 +3550,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="11">
         <v>44197</v>
       </c>
@@ -3656,7 +3656,7 @@
         <v>30.3</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="11">
         <v>44136</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="11">
         <v>44075</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="11">
         <v>44013</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="11">
         <v>43952</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="11">
         <v>43891</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>9.56</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>0.28999999999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="11">
         <v>43831</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>-5.19</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>45.7</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="11">
         <v>43770</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4451,7 +4451,7 @@
         <v>60.9</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="11">
         <v>43709</v>
       </c>
@@ -4504,7 +4504,7 @@
         <v>75.2</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>96.4</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="11">
         <v>43647</v>
       </c>
@@ -4610,7 +4610,7 @@
         <v>127.9</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>189.6</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="11">
         <v>43586</v>
       </c>
@@ -4716,7 +4716,7 @@
         <v>377.8</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4769,7 +4769,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="11">
         <v>43525</v>
       </c>
@@ -4822,7 +4822,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="11">
         <v>43466</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="11">
         <v>43405</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="11">
         <v>43344</v>
       </c>
@@ -5140,7 +5140,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="11">
         <v>43282</v>
       </c>
@@ -5246,7 +5246,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="11">
         <v>43221</v>
       </c>
@@ -5352,7 +5352,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5405,402 +5405,402 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" s="11">
         <v>45413</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" s="11">
         <v>45352</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" s="11">
         <v>45292</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" s="11">
         <v>45231</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" s="11">
         <v>45170</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" s="11">
         <v>45108</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" s="11">
         <v>45047</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" s="11">
         <v>44986</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" s="11">
         <v>44927</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" s="11">
         <v>44866</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A103" s="11">
         <v>44805</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A104" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A105" s="11">
         <v>44743</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A106" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A107" s="11">
         <v>44682</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A108" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A109" s="11">
         <v>44621</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A110" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A111" s="11">
         <v>44562</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A112" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" s="11">
         <v>44501</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A115" s="11">
         <v>44440</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A116" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A117" s="11">
         <v>44378</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A120" s="11">
         <v>44317</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A122" s="11">
         <v>44256</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A124" s="11">
         <v>44197</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A126" s="11">
         <v>44136</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A128" s="11">
         <v>44075</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A130" s="11">
         <v>44013</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A132" s="11">
         <v>43952</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A134" s="11">
         <v>43891</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A136" s="11">
         <v>43831</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A138" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A139" s="11">
         <v>43770</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A140" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A141" s="11">
         <v>43709</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A142" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A143" s="11">
         <v>43647</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A144" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A145" s="11">
         <v>43586</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A147" s="11">
         <v>43525</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A148" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A149" s="11">
         <v>43466</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A151" s="11">
         <v>43405</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A152" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A153" s="11">
         <v>43344</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A154" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A155" s="11">
         <v>43282</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A158" s="11">
         <v>43221</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>43191</v>
       </c>
